--- a/produtos_ua.xlsx
+++ b/produtos_ua.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI130"/>
+  <dimension ref="A1:AJ130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" style="11" min="1" max="1"/>
@@ -738,6 +738,11 @@
           <t>119D</t>
         </is>
       </c>
+      <c r="AJ1" s="7" t="inlineStr">
+        <is>
+          <t>CONTINUIDADE</t>
+        </is>
+      </c>
     </row>
     <row r="2" hidden="1" s="11">
       <c r="A2">
@@ -7678,6 +7683,11 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7728,6 +7738,11 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7943,6 +7958,11 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7993,6 +8013,11 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8098,6 +8123,11 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8148,6 +8178,11 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8198,6 +8233,11 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8468,6 +8508,11 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8573,6 +8618,11 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8898,6 +8948,11 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8948,6 +9003,11 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8996,6 +9056,11 @@
       <c r="L121" s="5" t="inlineStr">
         <is>
           <t>1S27</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>SIM</t>
         </is>
       </c>
     </row>

--- a/produtos_ua.xlsx
+++ b/produtos_ua.xlsx
@@ -6093,6 +6093,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S67" t="n">
+        <v>532.28</v>
+      </c>
+      <c r="T67" t="n">
+        <v>536.25</v>
+      </c>
+      <c r="U67" t="n">
+        <v>538.23</v>
+      </c>
+      <c r="V67" t="n">
+        <v>540.15</v>
+      </c>
+      <c r="W67" t="n">
+        <v>542.13</v>
+      </c>
+      <c r="X67" t="n">
+        <v>544.11</v>
+      </c>
+      <c r="Y67" t="n">
+        <v>546.09</v>
+      </c>
+      <c r="Z67" t="n">
+        <v>548.01</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>550</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>553.4</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>556.87</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>560.34</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>565.01</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>569.6799999999999</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>574.41</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>579.14</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>583.9299999999999</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -6148,6 +6199,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S68" t="n">
+        <v>532.28</v>
+      </c>
+      <c r="T68" t="n">
+        <v>536.25</v>
+      </c>
+      <c r="U68" t="n">
+        <v>538.23</v>
+      </c>
+      <c r="V68" t="n">
+        <v>540.15</v>
+      </c>
+      <c r="W68" t="n">
+        <v>542.13</v>
+      </c>
+      <c r="X68" t="n">
+        <v>544.11</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>546.09</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>548.01</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>550</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>553.4</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>556.87</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>560.34</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>565.01</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>569.6799999999999</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>574.41</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>579.14</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>583.9299999999999</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -6203,6 +6305,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S69" t="n">
+        <v>532.28</v>
+      </c>
+      <c r="T69" t="n">
+        <v>536.25</v>
+      </c>
+      <c r="U69" t="n">
+        <v>538.23</v>
+      </c>
+      <c r="V69" t="n">
+        <v>540.15</v>
+      </c>
+      <c r="W69" t="n">
+        <v>542.13</v>
+      </c>
+      <c r="X69" t="n">
+        <v>544.11</v>
+      </c>
+      <c r="Y69" t="n">
+        <v>546.09</v>
+      </c>
+      <c r="Z69" t="n">
+        <v>548.01</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>550</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>553.4</v>
+      </c>
+      <c r="AC69" t="n">
+        <v>556.87</v>
+      </c>
+      <c r="AD69" t="n">
+        <v>560.34</v>
+      </c>
+      <c r="AE69" t="n">
+        <v>565.01</v>
+      </c>
+      <c r="AF69" t="n">
+        <v>569.6799999999999</v>
+      </c>
+      <c r="AG69" t="n">
+        <v>574.41</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>579.14</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>583.9299999999999</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -6258,6 +6411,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S70" t="n">
+        <v>967.79</v>
+      </c>
+      <c r="T70" t="n">
+        <v>975</v>
+      </c>
+      <c r="U70" t="n">
+        <v>978.6</v>
+      </c>
+      <c r="V70" t="n">
+        <v>982.1</v>
+      </c>
+      <c r="W70" t="n">
+        <v>985.7</v>
+      </c>
+      <c r="X70" t="n">
+        <v>989.29</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>992.89</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>996.39</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>1006.2</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>1012.5</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>1018.79</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1027.3</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1035.8</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1044.39</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1052.99</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>1061.69</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -6313,6 +6517,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S71" t="n">
+        <v>532.28</v>
+      </c>
+      <c r="T71" t="n">
+        <v>536.25</v>
+      </c>
+      <c r="U71" t="n">
+        <v>538.23</v>
+      </c>
+      <c r="V71" t="n">
+        <v>540.15</v>
+      </c>
+      <c r="W71" t="n">
+        <v>542.13</v>
+      </c>
+      <c r="X71" t="n">
+        <v>544.11</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>546.09</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>548.01</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>550</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>553.4</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>556.87</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>560.34</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>565.01</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>569.6799999999999</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>574.41</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>579.14</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>583.9299999999999</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6368,6 +6623,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S72" t="n">
+        <v>532.28</v>
+      </c>
+      <c r="T72" t="n">
+        <v>536.25</v>
+      </c>
+      <c r="U72" t="n">
+        <v>538.23</v>
+      </c>
+      <c r="V72" t="n">
+        <v>540.15</v>
+      </c>
+      <c r="W72" t="n">
+        <v>542.13</v>
+      </c>
+      <c r="X72" t="n">
+        <v>544.11</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>546.09</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>548.01</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>550</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>553.4</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>556.87</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>560.34</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>565.01</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>569.6799999999999</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>574.41</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>579.14</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>583.9299999999999</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6423,6 +6729,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S73" t="n">
+        <v>677.46</v>
+      </c>
+      <c r="T73" t="n">
+        <v>682.49</v>
+      </c>
+      <c r="U73" t="n">
+        <v>685.01</v>
+      </c>
+      <c r="V73" t="n">
+        <v>687.47</v>
+      </c>
+      <c r="W73" t="n">
+        <v>689.99</v>
+      </c>
+      <c r="X73" t="n">
+        <v>692.5</v>
+      </c>
+      <c r="Y73" t="n">
+        <v>695.02</v>
+      </c>
+      <c r="Z73" t="n">
+        <v>697.48</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>704.34</v>
+      </c>
+      <c r="AC73" t="n">
+        <v>708.75</v>
+      </c>
+      <c r="AD73" t="n">
+        <v>713.15</v>
+      </c>
+      <c r="AE73" t="n">
+        <v>719.11</v>
+      </c>
+      <c r="AF73" t="n">
+        <v>725.05</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>731.08</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>737.1</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>743.1799999999999</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6478,6 +6835,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S74" t="n">
+        <v>677.46</v>
+      </c>
+      <c r="T74" t="n">
+        <v>682.49</v>
+      </c>
+      <c r="U74" t="n">
+        <v>685.01</v>
+      </c>
+      <c r="V74" t="n">
+        <v>687.47</v>
+      </c>
+      <c r="W74" t="n">
+        <v>689.99</v>
+      </c>
+      <c r="X74" t="n">
+        <v>692.5</v>
+      </c>
+      <c r="Y74" t="n">
+        <v>695.02</v>
+      </c>
+      <c r="Z74" t="n">
+        <v>697.48</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>704.34</v>
+      </c>
+      <c r="AC74" t="n">
+        <v>708.75</v>
+      </c>
+      <c r="AD74" t="n">
+        <v>713.15</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>719.11</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>725.05</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>731.08</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>737.1</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>743.1799999999999</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6533,6 +6941,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S75" t="n">
+        <v>677.46</v>
+      </c>
+      <c r="T75" t="n">
+        <v>682.49</v>
+      </c>
+      <c r="U75" t="n">
+        <v>685.01</v>
+      </c>
+      <c r="V75" t="n">
+        <v>687.47</v>
+      </c>
+      <c r="W75" t="n">
+        <v>689.99</v>
+      </c>
+      <c r="X75" t="n">
+        <v>692.5</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>695.02</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>697.48</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>704.34</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>708.75</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>713.15</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>719.11</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>725.05</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>731.08</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>737.1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>743.1799999999999</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6588,6 +7047,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S76" t="n">
+        <v>677.46</v>
+      </c>
+      <c r="T76" t="n">
+        <v>682.49</v>
+      </c>
+      <c r="U76" t="n">
+        <v>685.01</v>
+      </c>
+      <c r="V76" t="n">
+        <v>687.47</v>
+      </c>
+      <c r="W76" t="n">
+        <v>689.99</v>
+      </c>
+      <c r="X76" t="n">
+        <v>692.5</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>695.02</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>697.48</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>700</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>704.34</v>
+      </c>
+      <c r="AC76" t="n">
+        <v>708.75</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>713.15</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>719.11</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>725.05</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>731.08</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>737.1</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>743.1799999999999</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6643,6 +7153,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S77" t="n">
+        <v>338.73</v>
+      </c>
+      <c r="T77" t="n">
+        <v>341.24</v>
+      </c>
+      <c r="U77" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="V77" t="n">
+        <v>343.73</v>
+      </c>
+      <c r="W77" t="n">
+        <v>344.99</v>
+      </c>
+      <c r="X77" t="n">
+        <v>346.25</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>347.51</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>348.74</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>352.17</v>
+      </c>
+      <c r="AC77" t="n">
+        <v>354.37</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>359.55</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>362.52</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>368.55</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>371.59</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6698,6 +7259,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S78" t="n">
+        <v>338.73</v>
+      </c>
+      <c r="T78" t="n">
+        <v>341.24</v>
+      </c>
+      <c r="U78" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="V78" t="n">
+        <v>343.73</v>
+      </c>
+      <c r="W78" t="n">
+        <v>344.99</v>
+      </c>
+      <c r="X78" t="n">
+        <v>346.25</v>
+      </c>
+      <c r="Y78" t="n">
+        <v>347.51</v>
+      </c>
+      <c r="Z78" t="n">
+        <v>348.74</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>352.17</v>
+      </c>
+      <c r="AC78" t="n">
+        <v>354.37</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>359.55</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>362.52</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>368.55</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>371.59</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6753,6 +7365,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S79" t="n">
+        <v>338.73</v>
+      </c>
+      <c r="T79" t="n">
+        <v>341.24</v>
+      </c>
+      <c r="U79" t="n">
+        <v>342.5</v>
+      </c>
+      <c r="V79" t="n">
+        <v>343.73</v>
+      </c>
+      <c r="W79" t="n">
+        <v>344.99</v>
+      </c>
+      <c r="X79" t="n">
+        <v>346.25</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>347.51</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>348.74</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>350</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>352.17</v>
+      </c>
+      <c r="AC79" t="n">
+        <v>354.37</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>356.57</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>359.55</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>362.52</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>365.54</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>368.55</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>371.59</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6808,6 +7471,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S80" t="n">
+        <v>266.14</v>
+      </c>
+      <c r="T80" t="n">
+        <v>268.12</v>
+      </c>
+      <c r="U80" t="n">
+        <v>269.11</v>
+      </c>
+      <c r="V80" t="n">
+        <v>270.07</v>
+      </c>
+      <c r="W80" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="X80" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>273.04</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>274</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>275</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>278.43</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>280.17</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>284.84</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>289.57</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>291.96</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6863,6 +7577,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S81" t="n">
+        <v>266.14</v>
+      </c>
+      <c r="T81" t="n">
+        <v>268.12</v>
+      </c>
+      <c r="U81" t="n">
+        <v>269.11</v>
+      </c>
+      <c r="V81" t="n">
+        <v>270.07</v>
+      </c>
+      <c r="W81" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="X81" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>273.04</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>274</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>275</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="AC81" t="n">
+        <v>278.43</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>280.17</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>284.84</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>289.57</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>291.96</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6918,6 +7683,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S82" t="n">
+        <v>266.14</v>
+      </c>
+      <c r="T82" t="n">
+        <v>268.12</v>
+      </c>
+      <c r="U82" t="n">
+        <v>269.11</v>
+      </c>
+      <c r="V82" t="n">
+        <v>270.07</v>
+      </c>
+      <c r="W82" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="X82" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>273.04</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>274</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>275</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>278.43</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>280.17</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>284.84</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>289.57</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>291.96</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6973,6 +7789,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S83" t="n">
+        <v>266.14</v>
+      </c>
+      <c r="T83" t="n">
+        <v>268.12</v>
+      </c>
+      <c r="U83" t="n">
+        <v>269.11</v>
+      </c>
+      <c r="V83" t="n">
+        <v>270.07</v>
+      </c>
+      <c r="W83" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="X83" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="Y83" t="n">
+        <v>273.04</v>
+      </c>
+      <c r="Z83" t="n">
+        <v>274</v>
+      </c>
+      <c r="AA83" t="n">
+        <v>275</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="AC83" t="n">
+        <v>278.43</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>280.17</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>284.84</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>289.57</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>291.96</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -7028,6 +7895,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S84" t="n">
+        <v>241.94</v>
+      </c>
+      <c r="T84" t="n">
+        <v>243.75</v>
+      </c>
+      <c r="U84" t="n">
+        <v>244.65</v>
+      </c>
+      <c r="V84" t="n">
+        <v>245.52</v>
+      </c>
+      <c r="W84" t="n">
+        <v>246.42</v>
+      </c>
+      <c r="X84" t="n">
+        <v>247.32</v>
+      </c>
+      <c r="Y84" t="n">
+        <v>248.22</v>
+      </c>
+      <c r="Z84" t="n">
+        <v>249.09</v>
+      </c>
+      <c r="AA84" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>251.54</v>
+      </c>
+      <c r="AC84" t="n">
+        <v>253.12</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>254.69</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>256.82</v>
+      </c>
+      <c r="AF84" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>261.1</v>
+      </c>
+      <c r="AH84" t="n">
+        <v>263.25</v>
+      </c>
+      <c r="AI84" t="n">
+        <v>265.42</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7083,6 +8001,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S85" t="n">
+        <v>241.94</v>
+      </c>
+      <c r="T85" t="n">
+        <v>243.75</v>
+      </c>
+      <c r="U85" t="n">
+        <v>244.65</v>
+      </c>
+      <c r="V85" t="n">
+        <v>245.52</v>
+      </c>
+      <c r="W85" t="n">
+        <v>246.42</v>
+      </c>
+      <c r="X85" t="n">
+        <v>247.32</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>248.22</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>249.09</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>251.54</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>253.12</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>254.69</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>256.82</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>261.1</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>263.25</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>265.42</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7138,6 +8107,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S86" t="n">
+        <v>241.94</v>
+      </c>
+      <c r="T86" t="n">
+        <v>243.75</v>
+      </c>
+      <c r="U86" t="n">
+        <v>244.65</v>
+      </c>
+      <c r="V86" t="n">
+        <v>245.52</v>
+      </c>
+      <c r="W86" t="n">
+        <v>246.42</v>
+      </c>
+      <c r="X86" t="n">
+        <v>247.32</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>248.22</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>249.09</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>251.54</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>253.12</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>254.69</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>256.82</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>261.1</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>263.25</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>265.42</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7193,6 +8213,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S87" t="n">
+        <v>241.94</v>
+      </c>
+      <c r="T87" t="n">
+        <v>243.75</v>
+      </c>
+      <c r="U87" t="n">
+        <v>244.65</v>
+      </c>
+      <c r="V87" t="n">
+        <v>245.52</v>
+      </c>
+      <c r="W87" t="n">
+        <v>246.42</v>
+      </c>
+      <c r="X87" t="n">
+        <v>247.32</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>248.22</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>249.09</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>251.54</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>253.12</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>254.69</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>256.82</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>261.1</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>263.25</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>265.42</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7248,6 +8319,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S88" t="n">
+        <v>241.94</v>
+      </c>
+      <c r="T88" t="n">
+        <v>243.75</v>
+      </c>
+      <c r="U88" t="n">
+        <v>244.65</v>
+      </c>
+      <c r="V88" t="n">
+        <v>245.52</v>
+      </c>
+      <c r="W88" t="n">
+        <v>246.42</v>
+      </c>
+      <c r="X88" t="n">
+        <v>247.32</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>248.22</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>249.09</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>251.54</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>253.12</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>254.69</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>256.82</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>258.94</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>261.1</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>263.25</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>265.42</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7303,6 +8425,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S89" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T89" t="n">
+        <v>195</v>
+      </c>
+      <c r="U89" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V89" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W89" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X89" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y89" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z89" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA89" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC89" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD89" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE89" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF89" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH89" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI89" t="n">
+        <v>212.34</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7358,6 +8531,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S90" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T90" t="n">
+        <v>195</v>
+      </c>
+      <c r="U90" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V90" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W90" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X90" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA90" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC90" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD90" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE90" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF90" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH90" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI90" t="n">
+        <v>212.34</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7413,6 +8637,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S91" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T91" t="n">
+        <v>195</v>
+      </c>
+      <c r="U91" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V91" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W91" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X91" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y91" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z91" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA91" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC91" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD91" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE91" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF91" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH91" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI91" t="n">
+        <v>212.34</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7468,6 +8743,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S92" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T92" t="n">
+        <v>195</v>
+      </c>
+      <c r="U92" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V92" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W92" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X92" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA92" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC92" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD92" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE92" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF92" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH92" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI92" t="n">
+        <v>212.34</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7523,6 +8849,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S93" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T93" t="n">
+        <v>195</v>
+      </c>
+      <c r="U93" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V93" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W93" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X93" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y93" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z93" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA93" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC93" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD93" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE93" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF93" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>212.34</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7578,6 +8955,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S94" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T94" t="n">
+        <v>195</v>
+      </c>
+      <c r="U94" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V94" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W94" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X94" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y94" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z94" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA94" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC94" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD94" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE94" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF94" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH94" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI94" t="n">
+        <v>212.34</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7633,6 +9061,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S95" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T95" t="n">
+        <v>195</v>
+      </c>
+      <c r="U95" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V95" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W95" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X95" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>212.34</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7683,6 +9162,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S96" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T96" t="n">
+        <v>195</v>
+      </c>
+      <c r="U96" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V96" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W96" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X96" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y96" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z96" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA96" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC96" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD96" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE96" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF96" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH96" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI96" t="n">
+        <v>212.34</v>
+      </c>
       <c r="AJ96" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -7738,6 +9268,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S97" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T97" t="n">
+        <v>195</v>
+      </c>
+      <c r="U97" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V97" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W97" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X97" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y97" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z97" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA97" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC97" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD97" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE97" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF97" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH97" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI97" t="n">
+        <v>212.34</v>
+      </c>
       <c r="AJ97" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -7798,6 +9379,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S98" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T98" t="n">
+        <v>195</v>
+      </c>
+      <c r="U98" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V98" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W98" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X98" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y98" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z98" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA98" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC98" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD98" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE98" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF98" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH98" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI98" t="n">
+        <v>212.34</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7853,6 +9485,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S99" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T99" t="n">
+        <v>195</v>
+      </c>
+      <c r="U99" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V99" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W99" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X99" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y99" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z99" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA99" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC99" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD99" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF99" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH99" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI99" t="n">
+        <v>212.34</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7908,6 +9591,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S100" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T100" t="n">
+        <v>195</v>
+      </c>
+      <c r="U100" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V100" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W100" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X100" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE100" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF100" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH100" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI100" t="n">
+        <v>212.34</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7958,6 +9692,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S101" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T101" t="n">
+        <v>195</v>
+      </c>
+      <c r="U101" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V101" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W101" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X101" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC101" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD101" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE101" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF101" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH101" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI101" t="n">
+        <v>212.34</v>
+      </c>
       <c r="AJ101" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -8013,6 +9798,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S102" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T102" t="n">
+        <v>195</v>
+      </c>
+      <c r="U102" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V102" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W102" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X102" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y102" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z102" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA102" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC102" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD102" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE102" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF102" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH102" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI102" t="n">
+        <v>212.34</v>
+      </c>
       <c r="AJ102" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -8073,6 +9909,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S103" t="n">
+        <v>193.56</v>
+      </c>
+      <c r="T103" t="n">
+        <v>195</v>
+      </c>
+      <c r="U103" t="n">
+        <v>195.72</v>
+      </c>
+      <c r="V103" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="W103" t="n">
+        <v>197.13</v>
+      </c>
+      <c r="X103" t="n">
+        <v>197.85</v>
+      </c>
+      <c r="Y103" t="n">
+        <v>198.57</v>
+      </c>
+      <c r="Z103" t="n">
+        <v>199.28</v>
+      </c>
+      <c r="AA103" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>201.24</v>
+      </c>
+      <c r="AC103" t="n">
+        <v>202.5</v>
+      </c>
+      <c r="AD103" t="n">
+        <v>203.75</v>
+      </c>
+      <c r="AE103" t="n">
+        <v>205.46</v>
+      </c>
+      <c r="AF103" t="n">
+        <v>207.16</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>208.88</v>
+      </c>
+      <c r="AH103" t="n">
+        <v>210.59</v>
+      </c>
+      <c r="AI103" t="n">
+        <v>212.34</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8123,6 +10010,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S104" t="n">
+        <v>183.88</v>
+      </c>
+      <c r="T104" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="U104" t="n">
+        <v>185.93</v>
+      </c>
+      <c r="V104" t="n">
+        <v>186.59</v>
+      </c>
+      <c r="W104" t="n">
+        <v>187.28</v>
+      </c>
+      <c r="X104" t="n">
+        <v>187.96</v>
+      </c>
+      <c r="Y104" t="n">
+        <v>188.65</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>189.31</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>191.17</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>192.37</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>193.57</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>195.18</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>196.8</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>198.43</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>200.06</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>201.72</v>
+      </c>
       <c r="AJ104" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -8178,6 +10116,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S105" t="n">
+        <v>183.88</v>
+      </c>
+      <c r="T105" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="U105" t="n">
+        <v>185.93</v>
+      </c>
+      <c r="V105" t="n">
+        <v>186.59</v>
+      </c>
+      <c r="W105" t="n">
+        <v>187.28</v>
+      </c>
+      <c r="X105" t="n">
+        <v>187.96</v>
+      </c>
+      <c r="Y105" t="n">
+        <v>188.65</v>
+      </c>
+      <c r="Z105" t="n">
+        <v>189.31</v>
+      </c>
+      <c r="AA105" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>191.17</v>
+      </c>
+      <c r="AC105" t="n">
+        <v>192.37</v>
+      </c>
+      <c r="AD105" t="n">
+        <v>193.57</v>
+      </c>
+      <c r="AE105" t="n">
+        <v>195.18</v>
+      </c>
+      <c r="AF105" t="n">
+        <v>196.8</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>198.43</v>
+      </c>
+      <c r="AH105" t="n">
+        <v>200.06</v>
+      </c>
+      <c r="AI105" t="n">
+        <v>201.72</v>
+      </c>
       <c r="AJ105" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -8233,6 +10222,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S106" t="n">
+        <v>183.88</v>
+      </c>
+      <c r="T106" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="U106" t="n">
+        <v>185.93</v>
+      </c>
+      <c r="V106" t="n">
+        <v>186.59</v>
+      </c>
+      <c r="W106" t="n">
+        <v>187.28</v>
+      </c>
+      <c r="X106" t="n">
+        <v>187.96</v>
+      </c>
+      <c r="Y106" t="n">
+        <v>188.65</v>
+      </c>
+      <c r="Z106" t="n">
+        <v>189.31</v>
+      </c>
+      <c r="AA106" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>191.17</v>
+      </c>
+      <c r="AC106" t="n">
+        <v>192.37</v>
+      </c>
+      <c r="AD106" t="n">
+        <v>193.57</v>
+      </c>
+      <c r="AE106" t="n">
+        <v>195.18</v>
+      </c>
+      <c r="AF106" t="n">
+        <v>196.8</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>198.43</v>
+      </c>
+      <c r="AH106" t="n">
+        <v>200.06</v>
+      </c>
+      <c r="AI106" t="n">
+        <v>201.72</v>
+      </c>
       <c r="AJ106" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -8293,6 +10333,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S107" t="n">
+        <v>183.88</v>
+      </c>
+      <c r="T107" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="U107" t="n">
+        <v>185.93</v>
+      </c>
+      <c r="V107" t="n">
+        <v>186.59</v>
+      </c>
+      <c r="W107" t="n">
+        <v>187.28</v>
+      </c>
+      <c r="X107" t="n">
+        <v>187.96</v>
+      </c>
+      <c r="Y107" t="n">
+        <v>188.65</v>
+      </c>
+      <c r="Z107" t="n">
+        <v>189.31</v>
+      </c>
+      <c r="AA107" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>191.17</v>
+      </c>
+      <c r="AC107" t="n">
+        <v>192.37</v>
+      </c>
+      <c r="AD107" t="n">
+        <v>193.57</v>
+      </c>
+      <c r="AE107" t="n">
+        <v>195.18</v>
+      </c>
+      <c r="AF107" t="n">
+        <v>196.8</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>198.43</v>
+      </c>
+      <c r="AH107" t="n">
+        <v>200.06</v>
+      </c>
+      <c r="AI107" t="n">
+        <v>201.72</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8348,6 +10439,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S108" t="n">
+        <v>183.88</v>
+      </c>
+      <c r="T108" t="n">
+        <v>185.25</v>
+      </c>
+      <c r="U108" t="n">
+        <v>185.93</v>
+      </c>
+      <c r="V108" t="n">
+        <v>186.59</v>
+      </c>
+      <c r="W108" t="n">
+        <v>187.28</v>
+      </c>
+      <c r="X108" t="n">
+        <v>187.96</v>
+      </c>
+      <c r="Y108" t="n">
+        <v>188.65</v>
+      </c>
+      <c r="Z108" t="n">
+        <v>189.31</v>
+      </c>
+      <c r="AA108" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>191.17</v>
+      </c>
+      <c r="AC108" t="n">
+        <v>192.37</v>
+      </c>
+      <c r="AD108" t="n">
+        <v>193.57</v>
+      </c>
+      <c r="AE108" t="n">
+        <v>195.18</v>
+      </c>
+      <c r="AF108" t="n">
+        <v>196.8</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>198.43</v>
+      </c>
+      <c r="AH108" t="n">
+        <v>200.06</v>
+      </c>
+      <c r="AI108" t="n">
+        <v>201.72</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8403,6 +10545,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S109" t="n">
+        <v>174.2</v>
+      </c>
+      <c r="T109" t="n">
+        <v>175.49</v>
+      </c>
+      <c r="U109" t="n">
+        <v>176.14</v>
+      </c>
+      <c r="V109" t="n">
+        <v>176.77</v>
+      </c>
+      <c r="W109" t="n">
+        <v>177.42</v>
+      </c>
+      <c r="X109" t="n">
+        <v>178.07</v>
+      </c>
+      <c r="Y109" t="n">
+        <v>178.72</v>
+      </c>
+      <c r="Z109" t="n">
+        <v>179.35</v>
+      </c>
+      <c r="AA109" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>181.11</v>
+      </c>
+      <c r="AC109" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AD109" t="n">
+        <v>183.38</v>
+      </c>
+      <c r="AE109" t="n">
+        <v>184.91</v>
+      </c>
+      <c r="AF109" t="n">
+        <v>186.44</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>187.99</v>
+      </c>
+      <c r="AH109" t="n">
+        <v>189.53</v>
+      </c>
+      <c r="AI109" t="n">
+        <v>191.1</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8458,6 +10651,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S110" t="n">
+        <v>174.2</v>
+      </c>
+      <c r="T110" t="n">
+        <v>175.49</v>
+      </c>
+      <c r="U110" t="n">
+        <v>176.14</v>
+      </c>
+      <c r="V110" t="n">
+        <v>176.77</v>
+      </c>
+      <c r="W110" t="n">
+        <v>177.42</v>
+      </c>
+      <c r="X110" t="n">
+        <v>178.07</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>178.72</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>179.35</v>
+      </c>
+      <c r="AA110" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>181.11</v>
+      </c>
+      <c r="AC110" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>183.38</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>184.91</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>186.44</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>187.99</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>189.53</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>191.1</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8508,6 +10752,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S111" t="n">
+        <v>174.2</v>
+      </c>
+      <c r="T111" t="n">
+        <v>175.49</v>
+      </c>
+      <c r="U111" t="n">
+        <v>176.14</v>
+      </c>
+      <c r="V111" t="n">
+        <v>176.77</v>
+      </c>
+      <c r="W111" t="n">
+        <v>177.42</v>
+      </c>
+      <c r="X111" t="n">
+        <v>178.07</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>178.72</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>179.35</v>
+      </c>
+      <c r="AA111" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>181.11</v>
+      </c>
+      <c r="AC111" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>183.38</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>184.91</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>186.44</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>187.99</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>189.53</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>191.1</v>
+      </c>
       <c r="AJ111" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -8568,6 +10863,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S112" t="n">
+        <v>174.2</v>
+      </c>
+      <c r="T112" t="n">
+        <v>175.49</v>
+      </c>
+      <c r="U112" t="n">
+        <v>176.14</v>
+      </c>
+      <c r="V112" t="n">
+        <v>176.77</v>
+      </c>
+      <c r="W112" t="n">
+        <v>177.42</v>
+      </c>
+      <c r="X112" t="n">
+        <v>178.07</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>178.72</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>179.35</v>
+      </c>
+      <c r="AA112" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>181.11</v>
+      </c>
+      <c r="AC112" t="n">
+        <v>182.25</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>183.38</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>184.91</v>
+      </c>
+      <c r="AF112" t="n">
+        <v>186.44</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>187.99</v>
+      </c>
+      <c r="AH112" t="n">
+        <v>189.53</v>
+      </c>
+      <c r="AI112" t="n">
+        <v>191.1</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8618,6 +10964,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S113" t="n">
+        <v>290.33</v>
+      </c>
+      <c r="T113" t="n">
+        <v>292.49</v>
+      </c>
+      <c r="U113" t="n">
+        <v>293.57</v>
+      </c>
+      <c r="V113" t="n">
+        <v>294.62</v>
+      </c>
+      <c r="W113" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="X113" t="n">
+        <v>296.79</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>297.87</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>298.92</v>
+      </c>
+      <c r="AA113" t="n">
+        <v>300</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>301.86</v>
+      </c>
+      <c r="AC113" t="n">
+        <v>303.75</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>305.63</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>308.19</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>310.74</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>313.31</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>315.89</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>318.5</v>
+      </c>
       <c r="AJ113" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -8678,6 +11075,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S114" t="n">
+        <v>290.33</v>
+      </c>
+      <c r="T114" t="n">
+        <v>292.49</v>
+      </c>
+      <c r="U114" t="n">
+        <v>293.57</v>
+      </c>
+      <c r="V114" t="n">
+        <v>294.62</v>
+      </c>
+      <c r="W114" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="X114" t="n">
+        <v>296.79</v>
+      </c>
+      <c r="Y114" t="n">
+        <v>297.87</v>
+      </c>
+      <c r="Z114" t="n">
+        <v>298.92</v>
+      </c>
+      <c r="AA114" t="n">
+        <v>300</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>301.86</v>
+      </c>
+      <c r="AC114" t="n">
+        <v>303.75</v>
+      </c>
+      <c r="AD114" t="n">
+        <v>305.63</v>
+      </c>
+      <c r="AE114" t="n">
+        <v>308.19</v>
+      </c>
+      <c r="AF114" t="n">
+        <v>310.74</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>313.31</v>
+      </c>
+      <c r="AH114" t="n">
+        <v>315.89</v>
+      </c>
+      <c r="AI114" t="n">
+        <v>318.5</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8733,6 +11181,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S115" t="n">
+        <v>290.33</v>
+      </c>
+      <c r="T115" t="n">
+        <v>292.49</v>
+      </c>
+      <c r="U115" t="n">
+        <v>293.57</v>
+      </c>
+      <c r="V115" t="n">
+        <v>294.62</v>
+      </c>
+      <c r="W115" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="X115" t="n">
+        <v>296.79</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>297.87</v>
+      </c>
+      <c r="Z115" t="n">
+        <v>298.92</v>
+      </c>
+      <c r="AA115" t="n">
+        <v>300</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>301.86</v>
+      </c>
+      <c r="AC115" t="n">
+        <v>303.75</v>
+      </c>
+      <c r="AD115" t="n">
+        <v>305.63</v>
+      </c>
+      <c r="AE115" t="n">
+        <v>308.19</v>
+      </c>
+      <c r="AF115" t="n">
+        <v>310.74</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>313.31</v>
+      </c>
+      <c r="AH115" t="n">
+        <v>315.89</v>
+      </c>
+      <c r="AI115" t="n">
+        <v>318.5</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8788,6 +11287,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S116" t="n">
+        <v>290.33</v>
+      </c>
+      <c r="T116" t="n">
+        <v>292.49</v>
+      </c>
+      <c r="U116" t="n">
+        <v>293.57</v>
+      </c>
+      <c r="V116" t="n">
+        <v>294.62</v>
+      </c>
+      <c r="W116" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="X116" t="n">
+        <v>296.79</v>
+      </c>
+      <c r="Y116" t="n">
+        <v>297.87</v>
+      </c>
+      <c r="Z116" t="n">
+        <v>298.92</v>
+      </c>
+      <c r="AA116" t="n">
+        <v>300</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>301.86</v>
+      </c>
+      <c r="AC116" t="n">
+        <v>303.75</v>
+      </c>
+      <c r="AD116" t="n">
+        <v>305.63</v>
+      </c>
+      <c r="AE116" t="n">
+        <v>308.19</v>
+      </c>
+      <c r="AF116" t="n">
+        <v>310.74</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>313.31</v>
+      </c>
+      <c r="AH116" t="n">
+        <v>315.89</v>
+      </c>
+      <c r="AI116" t="n">
+        <v>318.5</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8843,6 +11393,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S117" t="n">
+        <v>266.14</v>
+      </c>
+      <c r="T117" t="n">
+        <v>268.12</v>
+      </c>
+      <c r="U117" t="n">
+        <v>269.11</v>
+      </c>
+      <c r="V117" t="n">
+        <v>270.07</v>
+      </c>
+      <c r="W117" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="X117" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>273.04</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>274</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>275</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>278.43</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>280.17</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>284.84</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>289.57</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>291.96</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8898,6 +11499,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S118" t="n">
+        <v>266.14</v>
+      </c>
+      <c r="T118" t="n">
+        <v>268.12</v>
+      </c>
+      <c r="U118" t="n">
+        <v>269.11</v>
+      </c>
+      <c r="V118" t="n">
+        <v>270.07</v>
+      </c>
+      <c r="W118" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="X118" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>273.04</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>274</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>275</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>278.43</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>280.17</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>284.84</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>289.57</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>291.96</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8948,6 +11600,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S119" t="n">
+        <v>266.14</v>
+      </c>
+      <c r="T119" t="n">
+        <v>268.12</v>
+      </c>
+      <c r="U119" t="n">
+        <v>269.11</v>
+      </c>
+      <c r="V119" t="n">
+        <v>270.07</v>
+      </c>
+      <c r="W119" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="X119" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>273.04</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>274</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>275</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>278.43</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>280.17</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>284.84</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>289.57</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>291.96</v>
+      </c>
       <c r="AJ119" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -9003,6 +11706,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S120" t="n">
+        <v>266.14</v>
+      </c>
+      <c r="T120" t="n">
+        <v>268.12</v>
+      </c>
+      <c r="U120" t="n">
+        <v>269.11</v>
+      </c>
+      <c r="V120" t="n">
+        <v>270.07</v>
+      </c>
+      <c r="W120" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="X120" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>273.04</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>274</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>275</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>278.43</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>280.17</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>284.84</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>289.57</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>291.96</v>
+      </c>
       <c r="AJ120" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -9058,6 +11812,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S121" t="n">
+        <v>266.14</v>
+      </c>
+      <c r="T121" t="n">
+        <v>268.12</v>
+      </c>
+      <c r="U121" t="n">
+        <v>269.11</v>
+      </c>
+      <c r="V121" t="n">
+        <v>270.07</v>
+      </c>
+      <c r="W121" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="X121" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>273.04</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>274</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>275</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>278.43</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>280.17</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>284.84</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>289.57</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>291.96</v>
+      </c>
       <c r="AJ121" t="inlineStr">
         <is>
           <t>SIM</t>
@@ -9118,6 +11923,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S122" t="n">
+        <v>266.14</v>
+      </c>
+      <c r="T122" t="n">
+        <v>268.12</v>
+      </c>
+      <c r="U122" t="n">
+        <v>269.11</v>
+      </c>
+      <c r="V122" t="n">
+        <v>270.07</v>
+      </c>
+      <c r="W122" t="n">
+        <v>271.06</v>
+      </c>
+      <c r="X122" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>273.04</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>274</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>275</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>276.7</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>278.43</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>280.17</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>282.5</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>284.84</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>287.2</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>289.57</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>291.96</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9173,6 +12029,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S123" t="n">
+        <v>120.97</v>
+      </c>
+      <c r="T123" t="n">
+        <v>121.87</v>
+      </c>
+      <c r="U123" t="n">
+        <v>122.32</v>
+      </c>
+      <c r="V123" t="n">
+        <v>122.76</v>
+      </c>
+      <c r="W123" t="n">
+        <v>123.21</v>
+      </c>
+      <c r="X123" t="n">
+        <v>123.66</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>124.11</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>125</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>125.77</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>126.56</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>127.34</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>128.41</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>129.47</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>130.54</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>131.62</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>132.71</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -9228,6 +12135,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S124" t="n">
+        <v>120.97</v>
+      </c>
+      <c r="T124" t="n">
+        <v>121.87</v>
+      </c>
+      <c r="U124" t="n">
+        <v>122.32</v>
+      </c>
+      <c r="V124" t="n">
+        <v>122.76</v>
+      </c>
+      <c r="W124" t="n">
+        <v>123.21</v>
+      </c>
+      <c r="X124" t="n">
+        <v>123.66</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>124.11</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>125</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>125.77</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>126.56</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>127.34</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>128.41</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>129.47</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>130.54</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>131.62</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>132.71</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -9283,6 +12241,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S125" t="n">
+        <v>120.97</v>
+      </c>
+      <c r="T125" t="n">
+        <v>121.87</v>
+      </c>
+      <c r="U125" t="n">
+        <v>122.32</v>
+      </c>
+      <c r="V125" t="n">
+        <v>122.76</v>
+      </c>
+      <c r="W125" t="n">
+        <v>123.21</v>
+      </c>
+      <c r="X125" t="n">
+        <v>123.66</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>124.11</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>125</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>125.77</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>126.56</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>127.34</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>128.41</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>129.47</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>130.54</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>131.62</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>132.71</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9338,6 +12347,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S126" t="n">
+        <v>120.97</v>
+      </c>
+      <c r="T126" t="n">
+        <v>121.87</v>
+      </c>
+      <c r="U126" t="n">
+        <v>122.32</v>
+      </c>
+      <c r="V126" t="n">
+        <v>122.76</v>
+      </c>
+      <c r="W126" t="n">
+        <v>123.21</v>
+      </c>
+      <c r="X126" t="n">
+        <v>123.66</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>124.11</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>124.55</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>125</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>125.77</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>126.56</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>127.34</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>128.41</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>129.47</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>130.54</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>131.62</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>132.71</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9393,6 +12453,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S127" t="n">
+        <v>96.78</v>
+      </c>
+      <c r="T127" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="U127" t="n">
+        <v>97.86</v>
+      </c>
+      <c r="V127" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="W127" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="X127" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>101.88</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>102.72</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>103.58</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>104.44</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>106.17</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9448,6 +12559,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S128" t="n">
+        <v>96.78</v>
+      </c>
+      <c r="T128" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="U128" t="n">
+        <v>97.86</v>
+      </c>
+      <c r="V128" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="W128" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="X128" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>101.88</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>102.72</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>103.58</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>104.44</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>106.17</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9503,6 +12665,57 @@
           <t>1S27</t>
         </is>
       </c>
+      <c r="S129" t="n">
+        <v>96.78</v>
+      </c>
+      <c r="T129" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="U129" t="n">
+        <v>97.86</v>
+      </c>
+      <c r="V129" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="W129" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="X129" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>101.88</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>102.72</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>103.58</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>104.44</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>106.17</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9557,6 +12770,57 @@
         <is>
           <t>1S27</t>
         </is>
+      </c>
+      <c r="S130" t="n">
+        <v>96.78</v>
+      </c>
+      <c r="T130" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="U130" t="n">
+        <v>97.86</v>
+      </c>
+      <c r="V130" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="W130" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="X130" t="n">
+        <v>98.92</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>99.28</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>99.64</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>100</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>100.61</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>101.25</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>101.88</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>102.72</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>103.58</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>104.44</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>105.3</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>106.17</v>
       </c>
     </row>
     <row r="131">
